--- a/data/trans_dic/IP1006-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1006-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen cardiopatía congénita</t>
+          <t>Menores que padecen cardiopatía congénita (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,65</t>
+          <t>0,25; 2,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,99</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,4</t>
+          <t>0,14; 1,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,04</t>
+          <t>0,11; 1,08</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,09</t>
+          <t>0,37; 3,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,36</t>
+          <t>0,17; 1,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,36</t>
+          <t>0,2; 2,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,94</t>
+          <t>0,1; 0,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,98</t>
+          <t>0,09; 0,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,78</t>
+          <t>0,09; 0,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,55</t>
+          <t>0,36; 1,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,82</t>
+          <t>0,08; 0,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,68</t>
+          <t>0,14; 0,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,89</t>
+          <t>0,26; 0,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,63</t>
+          <t>0,13; 0,65</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen cardiopatía congénita (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2708</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4476</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2939</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3705</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4142</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2658</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3440</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>675; 6710</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4461</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4868</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>678; 7370</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>537; 5040</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3325</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3003</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3618</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3971</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2775</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3033</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3156</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4663</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3361</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4917</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3471</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>654; 6728</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>660; 6114</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>697; 8039</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5499</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2510</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2673</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4610</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>7234</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4672</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>661; 5946</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4089</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>604; 6238</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>684; 6290</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2678; 11337</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>624; 5261</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1931; 9675</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3776; 13378</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1938; 9470</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1006-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1006-Edad-trans_dic.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,51</t>
+          <t>0,25; 2,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,1; 0,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,47</t>
+          <t>0,13; 1,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,08</t>
+          <t>0,11; 1,04</t>
         </is>
       </c>
     </row>
@@ -903,17 +903,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,27 +1008,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,78</t>
+          <t>0,37; 3,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,53</t>
+          <t>0,17; 1,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,3</t>
+          <t>0,19; 2,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,87</t>
+          <t>0,09; 0,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,89</t>
+          <t>0,09; 0,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,87</t>
+          <t>0,09; 0,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,52</t>
+          <t>0,37; 1,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,71</t>
+          <t>0,08; 0,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,69</t>
+          <t>0,15; 0,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,92</t>
+          <t>0,25; 0,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,65</t>
+          <t>0,14; 0,66</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2708</t>
+          <t>0; 2702</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4476</t>
+          <t>0; 3699</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2939</t>
+          <t>0; 2929</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3705</t>
+          <t>0; 4080</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4142</t>
+          <t>0; 4042</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1590,37 +1590,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2658</t>
+          <t>0; 2710</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3440</t>
+          <t>0; 3444</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>675; 6710</t>
+          <t>673; 6897</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4461</t>
+          <t>0; 4257</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4868</t>
+          <t>523; 4917</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>678; 7370</t>
+          <t>677; 6722</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>537; 5040</t>
+          <t>533; 4869</t>
         </is>
       </c>
     </row>
@@ -1748,17 +1748,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3325</t>
+          <t>0; 3441</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3003</t>
+          <t>0; 3425</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3618</t>
+          <t>0; 4914</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1773,17 +1773,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3971</t>
+          <t>0; 3597</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2775</t>
+          <t>0; 3455</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3033</t>
+          <t>0; 3006</t>
         </is>
       </c>
     </row>
@@ -1906,27 +1906,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4663</t>
+          <t>0; 4133</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3361</t>
+          <t>0; 3069</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4917</t>
+          <t>0; 5835</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3471</t>
+          <t>0; 3076</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>654; 6728</t>
+          <t>650; 6623</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>660; 6114</t>
+          <t>661; 6840</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>697; 8039</t>
+          <t>665; 7643</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5499</t>
+          <t>0; 5528</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>661; 5946</t>
+          <t>642; 5675</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4089</t>
+          <t>0; 4709</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>604; 6238</t>
+          <t>658; 6757</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>684; 6290</t>
+          <t>685; 5546</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2678; 11337</t>
+          <t>2740; 11705</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>624; 5261</t>
+          <t>626; 5491</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1931; 9675</t>
+          <t>2059; 9409</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3776; 13378</t>
+          <t>3570; 13035</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1938; 9470</t>
+          <t>2001; 9605</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1006-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1006-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,27 +630,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,29 +683,29 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,04</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,22</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,87</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,98</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,42 +788,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0,25; 2,65</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,77</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,59</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,29</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,36</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,25; 2,58</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,97</t>
+          <t>0,1; 0,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,34</t>
+          <t>0,13; 1,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,22</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,37; 4,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,72</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,71</t>
+          <t>0,16; 1,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,19</t>
+          <t>0,33; 2,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,83</t>
+          <t>0,09; 0,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0,33; 1,55</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,82</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,1; 0,94</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,67</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,96</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,77</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 1,56</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,74</t>
+          <t>0,09; 0,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,67</t>
+          <t>0,14; 0,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,9</t>
+          <t>0,26; 0,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,66</t>
+          <t>0,13; 0,63</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,27 +1316,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1369,27 +1369,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1422,29 +1422,29 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 2941</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4003</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2702</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3699</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2929</t>
+          <t>0; 2957</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4080</t>
+          <t>0; 4768</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1165</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2810</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1259</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4042</t>
+          <t>0; 4139</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>677; 7069</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4564</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4017</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2710</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3444</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>673; 6897</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4257</t>
+          <t>0; 2678</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>523; 4917</t>
+          <t>521; 5010</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>677; 6722</t>
+          <t>676; 7000</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>533; 4869</t>
+          <t>533; 4881</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>600</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 3392</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3441</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3425</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4914</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3816</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2979</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3597</t>
+          <t>0; 3626</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3455</t>
+          <t>0; 4086</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3006</t>
+          <t>0; 2996</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1344</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1537</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2495</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4133</t>
+          <t>0; 3483</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3069</t>
+          <t>655; 7274</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5835</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3076</t>
+          <t>0; 5322</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>650; 6623</t>
+          <t>0; 3673</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5518</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>661; 6840</t>
+          <t>660; 5458</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>665; 7643</t>
+          <t>1152; 8245</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5528</t>
+          <t>0; 5225</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2510</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1346</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2673</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>642; 5675</t>
+          <t>684; 5639</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4709</t>
+          <t>2501; 11602</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>658; 6757</t>
+          <t>627; 6071</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>685; 5546</t>
+          <t>665; 6411</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2740; 11705</t>
+          <t>0; 4746</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>626; 5491</t>
+          <t>602; 6913</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2059; 9409</t>
+          <t>2015; 9604</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3570; 13035</t>
+          <t>3851; 12979</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2001; 9605</t>
+          <t>1880; 9152</t>
         </is>
       </c>
     </row>
